--- a/東広島市_安芸津・黒瀬エリア3蔵_現行日本酒一覧.xlsx
+++ b/東広島市_安芸津・黒瀬エリア3蔵_現行日本酒一覧.xlsx
@@ -8,14 +8,18 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="現行商品一覧" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分類別集計" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="除外・統合一覧" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブランド一覧" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブランド・中核銘柄" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="現行商品一覧" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分類別集計" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="除外・統合一覧" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'現行商品一覧'!$A$4:$Q$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'分類別集計'!$A$4:$I$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'除外・統合一覧'!$A$4:$E$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ブランド一覧'!$A$4:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ブランド・中核銘柄'!$A$4:$R$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'現行商品一覧'!$A$4:$U$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'分類別集計'!$A$4:$I$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'除外・統合一覧'!$A$4:$E$104</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -207,33 +211,81 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_933542" displayName="T_933542" ref="A4:Q41" headerRowCount="1">
-  <autoFilter ref="A4:Q41"/>
-  <tableColumns count="17">
-    <tableColumn id="1" name="酒蔵"/>
-    <tableColumn id="2" name="商品名"/>
-    <tableColumn id="3" name="分類"/>
-    <tableColumn id="4" name="甘辛目安"/>
-    <tableColumn id="5" name="甘辛判定根拠"/>
-    <tableColumn id="6" name="日本酒度"/>
-    <tableColumn id="7" name="精米歩合"/>
-    <tableColumn id="8" name="アルコール度数"/>
-    <tableColumn id="9" name="おすすめの飲み方"/>
-    <tableColumn id="10" name="飲み方情報"/>
-    <tableColumn id="11" name="飲み方出典URL"/>
-    <tableColumn id="12" name="使用米"/>
-    <tableColumn id="13" name="容量"/>
-    <tableColumn id="14" name="参考価格"/>
-    <tableColumn id="15" name="流通区分"/>
-    <tableColumn id="16" name="備考"/>
-    <tableColumn id="17" name="出典URL"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_573163" displayName="T_573163" ref="A4:H10" headerRowCount="1">
+  <autoFilter ref="A4:H10"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="エリア"/>
+    <tableColumn id="2" name="酒蔵"/>
+    <tableColumn id="3" name="ブランド"/>
+    <tableColumn id="4" name="区分"/>
+    <tableColumn id="5" name="公式URL"/>
+    <tableColumn id="6" name="A中核銘柄数"/>
+    <tableColumn id="7" name="B主要銘柄数"/>
+    <tableColumn id="8" name="確認日"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_944508" displayName="T_944508" ref="A4:I7" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_839278" displayName="T_839278" ref="A4:R25" headerRowCount="1">
+  <autoFilter ref="A4:R25"/>
+  <tableColumns count="18">
+    <tableColumn id="1" name="エリア"/>
+    <tableColumn id="2" name="酒蔵"/>
+    <tableColumn id="3" name="ブランド"/>
+    <tableColumn id="4" name="シリーズ"/>
+    <tableColumn id="5" name="中核銘柄"/>
+    <tableColumn id="6" name="優先度"/>
+    <tableColumn id="7" name="位置づけ"/>
+    <tableColumn id="8" name="ブランド収録判定"/>
+    <tableColumn id="9" name="個別SKU確認"/>
+    <tableColumn id="10" name="分類"/>
+    <tableColumn id="11" name="甘辛目安"/>
+    <tableColumn id="12" name="日本酒度"/>
+    <tableColumn id="13" name="おすすめの飲み方"/>
+    <tableColumn id="14" name="主要容量"/>
+    <tableColumn id="15" name="流通区分"/>
+    <tableColumn id="16" name="確認日"/>
+    <tableColumn id="17" name="根拠URL"/>
+    <tableColumn id="18" name="商品出典URL"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T_270883" displayName="T_270883" ref="A4:U41" headerRowCount="1">
+  <autoFilter ref="A4:U41"/>
+  <tableColumns count="21">
+    <tableColumn id="1" name="酒蔵"/>
+    <tableColumn id="2" name="ブランド"/>
+    <tableColumn id="3" name="シリーズ"/>
+    <tableColumn id="4" name="ブランド優先度"/>
+    <tableColumn id="5" name="ブランド位置づけ"/>
+    <tableColumn id="6" name="商品名"/>
+    <tableColumn id="7" name="分類"/>
+    <tableColumn id="8" name="甘辛目安"/>
+    <tableColumn id="9" name="甘辛判定根拠"/>
+    <tableColumn id="10" name="日本酒度"/>
+    <tableColumn id="11" name="精米歩合"/>
+    <tableColumn id="12" name="アルコール度数"/>
+    <tableColumn id="13" name="おすすめの飲み方"/>
+    <tableColumn id="14" name="飲み方情報"/>
+    <tableColumn id="15" name="飲み方出典URL"/>
+    <tableColumn id="16" name="使用米"/>
+    <tableColumn id="17" name="容量"/>
+    <tableColumn id="18" name="参考価格"/>
+    <tableColumn id="19" name="流通区分"/>
+    <tableColumn id="20" name="備考"/>
+    <tableColumn id="21" name="出典URL"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T_900946" displayName="T_900946" ref="A4:I7" headerRowCount="1">
   <autoFilter ref="A4:I7"/>
   <tableColumns count="9">
     <tableColumn id="1" name="酒蔵"/>
@@ -250,9 +302,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T_708078" displayName="T_708078" ref="A4:E102" headerRowCount="1">
-  <autoFilter ref="A4:E102"/>
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T_964804" displayName="T_964804" ref="A4:E104" headerRowCount="1">
+  <autoFilter ref="A4:E104"/>
   <tableColumns count="5">
     <tableColumn id="1" name="酒蔵"/>
     <tableColumn id="2" name="元データ"/>
@@ -680,560 +732,956 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" min="15" max="15"/>
-    <col width="44" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>東広島市 安芸津・黒瀬エリア3蔵 現行日本酒一覧</t>
+          <t>東広島市 安芸津・黒瀬エリア3蔵 ブランド一覧</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>容量・包装違いは統合済み。生のSKU一覧ではなく、上司説明用の商品単位です。</t>
+          <t>主ブランド・別ブランド・主要シリーズを整理。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
+          <t>エリア</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
           <t>酒蔵</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>商品名</t>
-        </is>
-      </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>分類</t>
+          <t>ブランド</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>甘辛目安</t>
+          <t>区分</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>甘辛判定根拠</t>
+          <t>公式URL</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>日本酒度</t>
+          <t>A中核銘柄数</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>精米歩合</t>
+          <t>B主要銘柄数</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>アルコール度数</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>おすすめの飲み方</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>飲み方情報</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>飲み方出典URL</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>使用米</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>容量</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>参考価格</t>
-        </is>
-      </c>
-      <c r="O4" s="6" t="inlineStr">
-        <is>
-          <t>流通区分</t>
-        </is>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>出典URL</t>
+          <t>確認日</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>今田酒造本店</t>
+          <t>安芸津・黒瀬エリア3蔵</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>FUKUCHO LEGACY I</t>
+          <t>金光酒造</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>賀茂金秀</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>主ブランド</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>公開情報で判定材料不足</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>冷酒 / 常温</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>出典記載</t>
-        </is>
-      </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/legacy1</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>兵庫県特A地区山田錦 精米歩合 麹米 : 40% 掛米 : 40% アルコール分 16％ 酵母 広島県酵母 酒母 速醸 仕様 直汲み / 原酒 / 瓶火入れ /</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="inlineStr">
-        <is>
-          <t>500ml</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>33,000円</t>
-        </is>
-      </c>
-      <c r="O5" s="7" t="inlineStr">
-        <is>
-          <t>一般流通</t>
-        </is>
-      </c>
-      <c r="P5" s="7" t="inlineStr">
-        <is>
-          <t>公式オンラインショップで在庫あり</t>
-        </is>
-      </c>
-      <c r="Q5" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/legacy1</t>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>今田酒造本店</t>
+          <t>安芸津・黒瀬エリア3蔵</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>FUKUCHO LEGACY II</t>
+          <t>金光酒造</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>別ブランド</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>公開情報で判定材料不足</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr"/>
-      <c r="G6" s="9" t="inlineStr"/>
-      <c r="H6" s="9" t="inlineStr"/>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>冷酒 / 常温</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="inlineStr">
-        <is>
-          <t>出典記載</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/legacy2</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>兵庫県特A地区山田錦 精米歩合 麹米 : 40% 掛米 : 40% アルコール分 16％ 酵母 広島県酵母 酒母 速醸 仕様 直汲み / 原酒 / 瓶火入れ /</t>
-        </is>
-      </c>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>500ml</t>
-        </is>
-      </c>
-      <c r="N6" s="9" t="inlineStr">
-        <is>
-          <t>33,000円</t>
-        </is>
-      </c>
-      <c r="O6" s="9" t="inlineStr">
-        <is>
-          <t>一般流通</t>
-        </is>
-      </c>
-      <c r="P6" s="9" t="inlineStr">
-        <is>
-          <t>公式オンラインショップで在庫あり</t>
-        </is>
-      </c>
-      <c r="Q6" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/legacy2</t>
+          <t>https://www.kamokin.com/line_up/Limited/limited.html</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
           <t>今田酒造本店</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>八反草 サタケシリーズ GENKEI</t>
-        </is>
-      </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>富久長</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>主ブランド</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>公開情報で判定材料不足</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>冷酒</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>出典記載</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/hattansogenkei</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>広島県安芸高田市産八反草（契約栽培） 精米歩合 麹米 : 50% 掛米 : 60% 原形精米 アルコール分 15％ 酵母 広島県酵母 酒母 速醸 仕様 直汲み</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>720ml</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>2,200円</t>
-        </is>
-      </c>
-      <c r="O7" s="7" t="inlineStr">
-        <is>
-          <t>一般流通</t>
-        </is>
-      </c>
-      <c r="P7" s="7" t="inlineStr">
-        <is>
-          <t>公式オンラインショップで在庫あり</t>
-        </is>
-      </c>
-      <c r="Q7" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/hattansogenkei</t>
+          <t>https://fukucho.jp/</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
           <t>今田酒造本店</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>八反草 サタケシリーズ HENPEI</t>
-        </is>
-      </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>FUKUCHO LEGACY</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>海外・革新系シリーズ</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>公開情報で判定材料不足</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr"/>
-      <c r="G8" s="9" t="inlineStr"/>
-      <c r="H8" s="9" t="inlineStr"/>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>冷酒</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="inlineStr">
-        <is>
-          <t>出典記載</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/hattansohenpei</t>
-        </is>
-      </c>
-      <c r="L8" s="9" t="inlineStr">
-        <is>
-          <t>広島県安芸高田市産八反草（契約栽培） 精米歩合 麹米 : 50% 掛米 : 60% 扁平精米 アルコール分 15％ 酵母 広島県酵母 酒母 速醸 仕様 直汲み</t>
-        </is>
-      </c>
-      <c r="M8" s="9" t="inlineStr">
-        <is>
-          <t>720ml</t>
-        </is>
-      </c>
-      <c r="N8" s="9" t="inlineStr">
-        <is>
-          <t>2,200円</t>
-        </is>
-      </c>
-      <c r="O8" s="9" t="inlineStr">
-        <is>
-          <t>一般流通</t>
-        </is>
-      </c>
-      <c r="P8" s="9" t="inlineStr">
-        <is>
-          <t>公式オンラインショップで在庫あり</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/hattansohenpei</t>
+          <t>https://fukucho.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>今田酒造本店</t>
+          <t>安芸津・黒瀬エリア3蔵</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>八反草 純米 ハイブリッド生酛 特別栽培米R3</t>
+          <t>柄酒造</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>純米</t>
+          <t>9代目於多福</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>現行中心ブランド</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>公開情報で判定材料不足</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr"/>
-      <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr"/>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>冷酒 / 常温 / 燗酒</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>出典記載</t>
-        </is>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/hybridkimoto-r3-2021by</t>
-        </is>
-      </c>
-      <c r="L9" s="7" t="inlineStr">
-        <is>
-          <t>は唯一富久長が育てる広島在来品種の八反草</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="inlineStr">
-        <is>
-          <t>720ml</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
-          <t>2,420円</t>
-        </is>
-      </c>
-      <c r="O9" s="7" t="inlineStr">
-        <is>
-          <t>一般流通</t>
-        </is>
-      </c>
-      <c r="P9" s="7" t="inlineStr">
-        <is>
-          <t>公式オンラインショップで在庫あり</t>
-        </is>
-      </c>
-      <c r="Q9" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/hybridkimoto-r3-2021by</t>
+          <t>https://www.tsukasyuzou.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>今田酒造本店</t>
+          <t>安芸津・黒瀬エリア3蔵</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>八反草 純米 ハイブリッド生酛 特別栽培米R4</t>
+          <t>柄酒造</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>純米</t>
+          <t>於多福</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>従来主ブランド</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>公開情報で判定材料不足</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr"/>
-      <c r="G10" s="9" t="inlineStr"/>
-      <c r="H10" s="9" t="inlineStr"/>
+          <t>https://www.tsukasyuzou.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:H10"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="42" customWidth="1" min="17" max="17"/>
+    <col width="42" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>東広島市 安芸津・黒瀬エリア3蔵 ブランド・中核銘柄</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>A＝絶対に落とさない代表・蔵元推奨等、B＝主要定番・高級・注目ライン。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>エリア</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>酒蔵</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>ブランド</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>シリーズ</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>中核銘柄</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>優先度</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>位置づけ</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>ブランド収録判定</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>個別SKU確認</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>分類</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>甘辛目安</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>日本酒度</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>おすすめの飲み方</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>主要容量</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>流通区分</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>確認日</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>根拠URL</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>商品出典URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>金光酒造</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>賀茂金秀</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>賀茂金秀 純米大吟醸35</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>公式通年最高級ライン</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>中口</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>冷酒（10～15℃前後）</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>金光酒造</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>賀茂金秀</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr"/>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>賀茂金秀 純米大吟醸40</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>公式通年純米大吟醸</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>中口</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>冷酒（10～15℃前後）</t>
+        </is>
+      </c>
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O6" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P6" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q6" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+      <c r="R6" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>金光酒造</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>賀茂金秀</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>賀茂金秀 純米吟醸 雄町</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>公式通年・食との相性を訴求する代表銘柄</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>やや辛口</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>冷酒（10～15℃前後）</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>金光酒造</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>賀茂金秀</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr"/>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>賀茂金秀 特別純米</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>公式通年・「入魂の逸品」</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>特別純米</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>やや辛口</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>冷酒 / 燗酒（45～50℃）</t>
+        </is>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P8" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q8" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+      <c r="R8" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>金光酒造</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>賀茂金秀</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>賀茂金秀 特別純米 辛口</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>公式通年辛口ライン</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>特別純米</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>辛口</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>冷酒（10～15℃前後）</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+      <c r="R9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>金光酒造</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>賀茂金秀</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr"/>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>賀茂金秀 特別純米13</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>公式通年低アルコール系</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>冷酒 / 常温 / 燗酒</t>
+          <t>SKU確認済</t>
         </is>
       </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
-          <t>出典記載</t>
-        </is>
-      </c>
-      <c r="K10" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/hybridkimoto-r4-2022by</t>
+          <t>特別純米</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>中口</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>は唯一富久長が育てる広島在来品種の八反草</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>720ml</t>
+          <t>冷酒（5～15℃前後）</t>
         </is>
       </c>
       <c r="N10" s="9" t="inlineStr">
         <is>
-          <t>2,420円</t>
+          <t>720ml / 1,800ml</t>
         </is>
       </c>
       <c r="O10" s="9" t="inlineStr">
@@ -1243,151 +1691,169 @@
       </c>
       <c r="P10" s="9" t="inlineStr">
         <is>
-          <t>公式オンラインショップで在庫あり</t>
-        </is>
-      </c>
-      <c r="Q10" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/hybridkimoto-r4-2022by</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q10" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+      <c r="R10" s="9" t="inlineStr">
+        <is>
+          <t>https://j-s-p.or.jp/kuramoto/kanemitsu</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>今田酒造本店</t>
+          <t>安芸津・黒瀬エリア3蔵</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>八反草 純米 軟水仕込 辛口</t>
+          <t>金光酒造</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>純米</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>辛口</t>
-        </is>
-      </c>
+          <t>桜吹雪</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>商品名に辛口表記</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr"/>
-      <c r="G11" s="7" t="inlineStr"/>
-      <c r="H11" s="7" t="inlineStr"/>
+          <t>桜吹雪 特別純米うすにごり生</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>別ブランドの季節商品</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>冷酒 / 常温</t>
+          <t>SKU確認済</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>出典記載</t>
-        </is>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/hattansojunmai</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>広島県安芸高田市産八反草（契約栽培） 精米歩合 麹米 : 60% 掛米 : 65% 一部に真吟精米 アルコール分 14％ 酵母 広島県酵母 酒母 速醸 仕様 瓶</t>
-        </is>
-      </c>
+          <t>特別純米</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>720ml / 1,800ml</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>1,980～3,520円</t>
+          <t>1800ml</t>
         </is>
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>一般流通</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>公式オンラインショップで在庫あり</t>
-        </is>
-      </c>
-      <c r="Q11" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/hattansojunmai</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/Limited/limited.html</t>
+        </is>
+      </c>
+      <c r="R11" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/Limited/limited.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
           <t>今田酒造本店</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>海風土 Seafood 純米</t>
-        </is>
-      </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>純米</t>
+          <t>富久長</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
+          <t>八反草</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>富久長 八反草 純米吟醸</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>公式が唯一醸す八反草の中心ライン</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>公開情報で判定材料不足</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr"/>
-      <c r="G12" s="9" t="inlineStr"/>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>13度</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>冷酒 / 冷やして</t>
-        </is>
-      </c>
-      <c r="J12" s="9" t="inlineStr">
-        <is>
-          <t>出典記載</t>
-        </is>
-      </c>
-      <c r="K12" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/seafood</t>
-        </is>
-      </c>
-      <c r="L12" s="9" t="inlineStr">
-        <is>
-          <t>国産米 精米歩合 麹米 : 60% 掛米 : 70% アルコール分 13％ 酵母 広島県酵母 酒母 速醸 仕様 原酒 / 一回火入れ / 瓶貯蔵 おすすめ温度</t>
-        </is>
-      </c>
+      <c r="L12" s="9" t="inlineStr"/>
       <c r="M12" s="9" t="inlineStr">
         <is>
-          <t>500ml / 720ml / 1,800ml</t>
+          <t>冷酒</t>
         </is>
       </c>
       <c r="N12" s="9" t="inlineStr">
         <is>
-          <t>1,870～3,850円</t>
+          <t>720ml / 1,800ml</t>
         </is>
       </c>
       <c r="O12" s="9" t="inlineStr">
@@ -1397,147 +1863,169 @@
       </c>
       <c r="P12" s="9" t="inlineStr">
         <is>
-          <t>公式オンラインショップで在庫あり</t>
-        </is>
-      </c>
-      <c r="Q12" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/seafood</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q12" s="9" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/</t>
+        </is>
+      </c>
+      <c r="R12" s="9" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/hattanso-junmaiginjo</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
           <t>今田酒造本店</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>秋櫻〈コスモス〉 純米 ひやおろし</t>
-        </is>
-      </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>海風土</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>富久長 海風土 Seafood 純米</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>公式が海風土シリーズを中心ラインとして訴求</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
           <t>純米</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>公開情報で判定材料不足</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr"/>
-      <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="7" t="inlineStr"/>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>冷酒 / 常温</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>出典記載</t>
-        </is>
-      </c>
-      <c r="K13" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/cosmos</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>広島県東広島市産山田錦 / 兵庫県特A地区山田錦 / 広島県産米 精米歩合 麹米 : 60% 掛米 : 60% アルコール分 15％ 酵母 広島県酵母 酒母 速</t>
-        </is>
-      </c>
+      <c r="L13" s="7" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr">
         <is>
+          <t>冷酒 / 冷やして</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
           <t>720ml / 1,800ml</t>
         </is>
       </c>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>1,870～3,850円</t>
-        </is>
-      </c>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>季節商品</t>
+          <t>一般流通</t>
         </is>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>公式オンラインショップで在庫あり / 二次DBでも存在確認</t>
-        </is>
-      </c>
-      <c r="Q13" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/cosmos</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/</t>
+        </is>
+      </c>
+      <c r="R13" s="7" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/seafood</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
           <t>今田酒造本店</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>純米にごり スパークリング 白美 HAKUBI</t>
-        </is>
-      </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>純米</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr"/>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>富久長 純米吟醸 美穂 Biho</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>公式現行主要商品</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>公開情報で判定材料不足</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr"/>
-      <c r="G14" s="9" t="inlineStr"/>
-      <c r="H14" s="9" t="inlineStr"/>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>冷酒 / 常温</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="inlineStr">
-        <is>
-          <t>出典記載</t>
-        </is>
-      </c>
-      <c r="K14" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/hakubi</t>
-        </is>
-      </c>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>広島県東広島市産山田錦 / 兵庫県特A地区山田錦 / 広島県産米 精米歩合 麹米 : 60% 掛米 : 65% アルコール分 14％ 酵母 広島県酵母 酒母 速</t>
-        </is>
-      </c>
+      <c r="L14" s="9" t="inlineStr"/>
       <c r="M14" s="9" t="inlineStr">
         <is>
-          <t>500ml</t>
+          <t>冷酒</t>
         </is>
       </c>
       <c r="N14" s="9" t="inlineStr">
         <is>
-          <t>1,870円</t>
+          <t>720ml / 1,800ml</t>
         </is>
       </c>
       <c r="O14" s="9" t="inlineStr">
@@ -1547,74 +2035,83 @@
       </c>
       <c r="P14" s="9" t="inlineStr">
         <is>
-          <t>公式オンラインショップで在庫あり</t>
-        </is>
-      </c>
-      <c r="Q14" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/hakubi</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q14" s="9" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="R14" s="9" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/biho</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
           <t>今田酒造本店</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>辛口純米</t>
-        </is>
-      </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>富久長 辛口純米</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>公式現行定番</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
           <t>純米</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>辛口</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>商品名に辛口表記</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="7" t="inlineStr"/>
-      <c r="H15" s="7" t="inlineStr"/>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="L15" s="7" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>冷酒 / 常温 / 燗酒</t>
         </is>
       </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>出典記載</t>
-        </is>
-      </c>
-      <c r="K15" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/karakuchi</t>
-        </is>
-      </c>
-      <c r="L15" s="7" t="inlineStr">
-        <is>
-          <t>の一部に原形精米（真吟）のお米を使用しました</t>
-        </is>
-      </c>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="N15" s="7" t="inlineStr">
         <is>
           <t>720ml / 1,800ml</t>
         </is>
       </c>
-      <c r="N15" s="7" t="inlineStr">
-        <is>
-          <t>1,980～3,300円</t>
-        </is>
-      </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
           <t>一般流通</t>
@@ -1622,10 +2119,15 @@
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>公式オンラインショップで在庫あり / 二次DBでも存在確認</t>
-        </is>
-      </c>
-      <c r="Q15" s="8" t="inlineStr">
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="R15" s="7" t="inlineStr">
         <is>
           <t>https://fukucho.jp/products/karakuchi</t>
         </is>
@@ -1634,60 +2136,68 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
           <t>今田酒造本店</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>八反草 純米吟醸</t>
-        </is>
-      </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>純米吟醸</t>
+          <t>富久長</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
+          <t>八反草</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>富久長 八反草 純米大吟醸 妙花風</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>公式トップおすすめ商品に掲載する八反草上位酒</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>公開情報で判定材料不足</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr"/>
-      <c r="G16" s="9" t="inlineStr"/>
-      <c r="H16" s="9" t="inlineStr"/>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="L16" s="9" t="inlineStr"/>
+      <c r="M16" s="9" t="inlineStr">
         <is>
           <t>冷酒</t>
         </is>
       </c>
-      <c r="J16" s="9" t="inlineStr">
-        <is>
-          <t>出典記載</t>
-        </is>
-      </c>
-      <c r="K16" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/hattanso-junmaiginjo</t>
-        </is>
-      </c>
-      <c r="L16" s="9" t="inlineStr">
-        <is>
-          <t>広島県安芸高田市産八反草（契約栽培） 精米歩合 麹米 : 50% 掛米 : 60% アルコール分 15％ 酵母 広島県酵母 酒母 速醸 仕様 直汲み / 原酒</t>
-        </is>
-      </c>
-      <c r="M16" s="9" t="inlineStr">
-        <is>
-          <t>720ml / 1,800ml</t>
-        </is>
-      </c>
       <c r="N16" s="9" t="inlineStr">
         <is>
-          <t>2,200～4,290円</t>
+          <t>720ml</t>
         </is>
       </c>
       <c r="O16" s="9" t="inlineStr">
@@ -1697,72 +2207,85 @@
       </c>
       <c r="P16" s="9" t="inlineStr">
         <is>
-          <t>公式オンラインショップで在庫あり / 二次DBでも存在確認</t>
-        </is>
-      </c>
-      <c r="Q16" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/hattanso-junmaiginjo</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q16" s="9" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/</t>
+        </is>
+      </c>
+      <c r="R16" s="9" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/daiginjo_myokafu</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
           <t>今田酒造本店</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>八反草 純米吟醸 ハイブリッド生酛</t>
-        </is>
-      </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>純米吟醸</t>
+          <t>富久長</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
+          <t>八反草 サタケシリーズ</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>富久長 八反草 サタケシリーズ HENPEI</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>公式おすすめ・サタケ精米シリーズ</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>公開情報で判定材料不足</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr"/>
-      <c r="G17" s="7" t="inlineStr"/>
-      <c r="H17" s="7" t="inlineStr"/>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>冷酒 / 常温</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>出典記載</t>
-        </is>
-      </c>
-      <c r="K17" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/hybridkimoto-junmaiginjo</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="inlineStr">
-        <is>
-          <t>広島県安芸高田市産八反草（契約栽培） 精米歩合 麹米 : 50% 掛米 : 60% アルコール分 15％ 酵母 広島県酵母 酒母 ハイブリッド生酛 仕様 原酒</t>
-        </is>
-      </c>
+      <c r="L17" s="7" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>720ml / 1,800ml</t>
+          <t>冷酒</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>2,200～4,290円</t>
+          <t>720ml</t>
         </is>
       </c>
       <c r="O17" s="7" t="inlineStr">
@@ -1772,72 +2295,85 @@
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>公式オンラインショップで在庫あり</t>
-        </is>
-      </c>
-      <c r="Q17" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/hybridkimoto-junmaiginjo</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/</t>
+        </is>
+      </c>
+      <c r="R17" s="7" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/hattansohenpei</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
           <t>今田酒造本店</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>山田錦 純米吟醸</t>
-        </is>
-      </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>純米吟醸</t>
+          <t>富久長</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
+          <t>白美</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>富久長 純米にごり スパークリング 白美 HAKUBI</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>現行スパークリング主要商品</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>公開情報で判定材料不足</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr"/>
-      <c r="G18" s="9" t="inlineStr"/>
-      <c r="H18" s="9" t="inlineStr"/>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>冷酒</t>
-        </is>
-      </c>
-      <c r="J18" s="9" t="inlineStr">
-        <is>
-          <t>出典記載</t>
-        </is>
-      </c>
-      <c r="K18" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/yamadanishiki-junmaiginjo</t>
-        </is>
-      </c>
-      <c r="L18" s="9" t="inlineStr">
-        <is>
-          <t>広島県東広島市産山田錦 / 兵庫県特A地区山田錦 精米歩合 麹米 : 50% 掛米 : 60% アルコール分 16％ 酵母 広島県酵母のブレンド 酒母 速醸 仕</t>
-        </is>
-      </c>
+      <c r="L18" s="9" t="inlineStr"/>
       <c r="M18" s="9" t="inlineStr">
         <is>
-          <t>720ml / 1,800ml</t>
+          <t>冷酒 / 常温</t>
         </is>
       </c>
       <c r="N18" s="9" t="inlineStr">
         <is>
-          <t>2,200～4,290円</t>
+          <t>500ml</t>
         </is>
       </c>
       <c r="O18" s="9" t="inlineStr">
@@ -1847,149 +2383,167 @@
       </c>
       <c r="P18" s="9" t="inlineStr">
         <is>
-          <t>公式オンラインショップで在庫あり / 二次DBでも存在確認</t>
-        </is>
-      </c>
-      <c r="Q18" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/yamadanishiki-junmaiginjo</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q18" s="9" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="R18" s="9" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/hakubi</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>今田酒造本店</t>
+          <t>安芸津・黒瀬エリア3蔵</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>秋櫻〈コスモス〉 純米吟醸 ひやおろし</t>
+          <t>柄酒造</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>純米吟醸</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
+          <t>9代目於多福</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>9代目於多福 純米大吟醸</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>現行中心シリーズの上位酒</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>公開情報で判定材料不足</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr"/>
-      <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>冷酒</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>出典記載</t>
-        </is>
-      </c>
-      <c r="K19" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/cosmos-junmaiginjo</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="inlineStr">
-        <is>
-          <t>広島県東広島市産山田錦 / 兵庫県特A地区山田錦 / 広島県産米 精米歩合 麹米 : 50% 掛米 : 60% アルコール分 15％ 酵母 広島県酵母 酒母 速</t>
-        </is>
-      </c>
+      <c r="L19" s="7" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr">
         <is>
+          <t>冷酒 / 常温 / 熱燗</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
           <t>720ml / 1,800ml</t>
         </is>
       </c>
-      <c r="N19" s="7" t="inlineStr">
-        <is>
-          <t>1,870～3,850円</t>
-        </is>
-      </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>季節商品</t>
+          <t>一般流通</t>
         </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>公式オンラインショップで在庫あり / 二次DBでも存在確認</t>
-        </is>
-      </c>
-      <c r="Q19" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/cosmos-junmaiginjo</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="R19" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/products/於多福-純米-1800ml</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>今田酒造本店</t>
+          <t>安芸津・黒瀬エリア3蔵</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>純米吟醸 美穂 Biho</t>
+          <t>柄酒造</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
+          <t>9代目於多福</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr"/>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>9代目於多福 純米吟醸</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>現行中心シリーズ</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
           <t>純米吟醸</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>公開情報で判定材料不足</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr"/>
-      <c r="G20" s="9" t="inlineStr"/>
-      <c r="H20" s="9" t="inlineStr"/>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>冷酒</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="inlineStr">
-        <is>
-          <t>出典記載</t>
-        </is>
-      </c>
-      <c r="K20" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/biho</t>
-        </is>
-      </c>
-      <c r="L20" s="9" t="inlineStr">
-        <is>
-          <t>広島県東広島市産山田錦 / 兵庫県特A地区山田錦 / 広島県産米 精米歩合 麹米 : 50% 掛米 : 60% アルコール分 15％ 酵母 広島県酵母 酒母 速</t>
-        </is>
-      </c>
+      <c r="L20" s="9" t="inlineStr"/>
       <c r="M20" s="9" t="inlineStr">
         <is>
+          <t>冷酒 / 常温 / 熱燗</t>
+        </is>
+      </c>
+      <c r="N20" s="9" t="inlineStr">
+        <is>
           <t>720ml / 1,800ml</t>
         </is>
       </c>
-      <c r="N20" s="9" t="inlineStr">
-        <is>
-          <t>2,090～3,960円</t>
-        </is>
-      </c>
       <c r="O20" s="9" t="inlineStr">
         <is>
           <t>一般流通</t>
@@ -1997,74 +2551,83 @@
       </c>
       <c r="P20" s="9" t="inlineStr">
         <is>
-          <t>公式オンラインショップで在庫あり</t>
-        </is>
-      </c>
-      <c r="Q20" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/biho</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q20" s="9" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="R20" s="9" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/products/於多福-純米-1800ml</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>今田酒造本店</t>
+          <t>安芸津・黒瀬エリア3蔵</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>八反草 純米大吟醸</t>
+          <t>柄酒造</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>純米大吟醸</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
+          <t>9代目於多福</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>9代目於多福 純米</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>現行中心シリーズ</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>公開情報で判定材料不足</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr"/>
-      <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>冷酒</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>出典記載</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/daiginjo</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
-        <is>
-          <t>は種もみから復活させた広島最古の酒米の在来品種、八反草を減農薬、減肥料で育てました</t>
-        </is>
-      </c>
+      <c r="L21" s="7" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr">
         <is>
+          <t>冷酒 / 常温</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
           <t>720ml / 1,800ml</t>
         </is>
       </c>
-      <c r="N21" s="7" t="inlineStr">
-        <is>
-          <t>2,200～13,200円</t>
-        </is>
-      </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
           <t>一般流通</t>
@@ -2072,72 +2635,81 @@
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>公式オンラインショップで在庫あり</t>
-        </is>
-      </c>
-      <c r="Q21" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/daiginjo</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="R21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/products/火入れ-9代目於多福-純米</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>今田酒造本店</t>
+          <t>安芸津・黒瀬エリア3蔵</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>八反草 純米大吟醸 はしり</t>
+          <t>柄酒造</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>純米大吟醸</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
+          <t>於多福</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr"/>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>於多福 大吟醸</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>従来主ブランドの上位定番</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>大吟醸</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>公開情報で判定材料不足</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr"/>
-      <c r="G22" s="9" t="inlineStr"/>
-      <c r="H22" s="9" t="inlineStr"/>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>冷酒</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="inlineStr">
-        <is>
-          <t>出典記載</t>
-        </is>
-      </c>
-      <c r="K22" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/daiginjo_hashiri</t>
-        </is>
-      </c>
-      <c r="L22" s="9" t="inlineStr">
-        <is>
-          <t>は種もみから復活させた広島最古の酒米の在来品種、八反草を減農薬、減肥料で育てました</t>
-        </is>
-      </c>
+      <c r="L22" s="9" t="inlineStr"/>
       <c r="M22" s="9" t="inlineStr">
         <is>
-          <t>720ml</t>
+          <t>冷酒 / 常温</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
         <is>
-          <t>6,600円</t>
+          <t>720ml / 1,800ml</t>
         </is>
       </c>
       <c r="O22" s="9" t="inlineStr">
@@ -2147,72 +2719,81 @@
       </c>
       <c r="P22" s="9" t="inlineStr">
         <is>
-          <t>公式オンラインショップで在庫あり</t>
-        </is>
-      </c>
-      <c r="Q22" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/daiginjo_hashiri</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q22" s="9" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="R22" s="9" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/products/於多福-大吟醸-1800ml</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>今田酒造本店</t>
+          <t>安芸津・黒瀬エリア3蔵</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>八反草 純米大吟醸 妙花風</t>
+          <t>柄酒造</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>純米大吟醸</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
+          <t>於多福</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr"/>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>於多福 純米吟醸</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>従来主ブランドの主要商品</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>公開情報で判定材料不足</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>冷酒</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>出典記載</t>
-        </is>
-      </c>
-      <c r="K23" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/daiginjo_myokafu</t>
-        </is>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>は種もみから復活させた広島最古の酒米の在来品種、八反草を減農薬、減肥料で育てました</t>
-        </is>
-      </c>
+      <c r="L23" s="7" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>720ml</t>
+          <t>冷酒 / 冷やして / 常温</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>13,200円</t>
+          <t>720ml / 1,800ml</t>
         </is>
       </c>
       <c r="O23" s="7" t="inlineStr">
@@ -2222,82 +2803,83 @@
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>公式オンラインショップで在庫あり</t>
-        </is>
-      </c>
-      <c r="Q23" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/daiginjo_myokafu</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="R23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/products/於多福-純米吟醸-1800ml</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
           <t>柄酒造</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>9代目於多福 protos. 火入れ</t>
-        </is>
-      </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
+          <t>9代目於多福</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr"/>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>9代目於多福 特別純米</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>現行中心シリーズ</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>特別純米</t>
+        </is>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>公開情報で判定材料不足</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr"/>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>７１%</t>
-        </is>
-      </c>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>１３度</t>
-        </is>
-      </c>
-      <c r="I24" s="9" t="inlineStr">
+      <c r="L24" s="9" t="inlineStr"/>
+      <c r="M24" s="9" t="inlineStr">
         <is>
           <t>冷酒 / 常温</t>
         </is>
       </c>
-      <c r="J24" s="9" t="inlineStr">
-        <is>
-          <t>現行酒販店商品情報</t>
-        </is>
-      </c>
-      <c r="K24" s="8" t="inlineStr">
-        <is>
-          <t>https://tawawasake.base.shop/items/134292512</t>
-        </is>
-      </c>
-      <c r="L24" s="9" t="inlineStr">
-        <is>
-          <t>八反錦 精米歩合：７１% アルコール度数：１３度 酵母：協会７号 もろみ日数：41日 (71、13、7、41、全て素数です） {"id":91895203104</t>
-        </is>
-      </c>
-      <c r="M24" s="9" t="inlineStr">
+      <c r="N24" s="9" t="inlineStr">
         <is>
           <t>720ml</t>
         </is>
       </c>
-      <c r="N24" s="9" t="inlineStr">
-        <is>
-          <t>1,980円</t>
-        </is>
-      </c>
       <c r="O24" s="9" t="inlineStr">
         <is>
           <t>一般流通</t>
@@ -2305,93 +2887,2152 @@
       </c>
       <c r="P24" s="9" t="inlineStr">
         <is>
-          <t>公式オンラインショップで販売確認</t>
-        </is>
-      </c>
-      <c r="Q24" s="8" t="inlineStr">
-        <is>
-          <t>https://www.tsukasyuzou.jp/products/9代目於多福-protos-720ml-火入れ</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q24" s="9" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="R24" s="9" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/products/火入れ-9代目於多福-特別純米</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
           <t>柄酒造</t>
         </is>
       </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>於多福</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr"/>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>於多福 一番取り</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>従来ブランド高級ライン</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>冷酒</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="R25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/products/関西一-一番取り-720ml</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:R25"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A1:R1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="42" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>東広島市 安芸津・黒瀬エリア3蔵 現行日本酒一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>ブランド→商品→SKUの階層で整理。容量・包装違いは商品単位に統合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>酒蔵</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>ブランド</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>シリーズ</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>ブランド優先度</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>ブランド位置づけ</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>商品名</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>分類</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>甘辛目安</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>甘辛判定根拠</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>日本酒度</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>精米歩合</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>アルコール度数</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>おすすめの飲み方</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>飲み方情報</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>飲み方出典URL</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>使用米</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>容量</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>参考価格</t>
+        </is>
+      </c>
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>流通区分</t>
+        </is>
+      </c>
+      <c r="T4" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="U4" s="6" t="inlineStr">
+        <is>
+          <t>出典URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>今田酒造本店</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>FUKUCHO LEGACY</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>FUKUCHO LEGACY I</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>公開情報で判定材料不足</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr"/>
+      <c r="K5" s="7" t="inlineStr"/>
+      <c r="L5" s="7" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>出典記載</t>
+        </is>
+      </c>
+      <c r="O5" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/legacy1</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>兵庫県特A地区山田錦 精米歩合 麹米 : 40% 掛米 : 40% アルコール分 16％ 酵母 広島県酵母 酒母 速醸 仕様 直汲み / 原酒 / 瓶火入れ /</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>33,000円</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="T5" s="7" t="inlineStr">
+        <is>
+          <t>公式オンラインショップで在庫あり</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/legacy1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>今田酒造本店</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>FUKUCHO LEGACY</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr"/>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr"/>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>FUKUCHO LEGACY II</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>公開情報で判定材料不足</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr"/>
+      <c r="K6" s="9" t="inlineStr"/>
+      <c r="L6" s="9" t="inlineStr"/>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温</t>
+        </is>
+      </c>
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t>出典記載</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/legacy2</t>
+        </is>
+      </c>
+      <c r="P6" s="9" t="inlineStr">
+        <is>
+          <t>兵庫県特A地区山田錦 精米歩合 麹米 : 40% 掛米 : 40% アルコール分 16％ 酵母 広島県酵母 酒母 速醸 仕様 直汲み / 原酒 / 瓶火入れ /</t>
+        </is>
+      </c>
+      <c r="Q6" s="9" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
+      <c r="R6" s="9" t="inlineStr">
+        <is>
+          <t>33,000円</t>
+        </is>
+      </c>
+      <c r="S6" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="T6" s="9" t="inlineStr">
+        <is>
+          <t>公式オンラインショップで在庫あり</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/legacy2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>今田酒造本店</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>公式おすすめ・サタケ精米シリーズ</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>八反草 サタケシリーズ GENKEI</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>公開情報で判定材料不足</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr"/>
+      <c r="K7" s="7" t="inlineStr"/>
+      <c r="L7" s="7" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>冷酒</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>出典記載</t>
+        </is>
+      </c>
+      <c r="O7" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/hattansogenkei</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>広島県安芸高田市産八反草（契約栽培） 精米歩合 麹米 : 50% 掛米 : 60% 原形精米 アルコール分 15％ 酵母 広島県酵母 酒母 速醸 仕様 直汲み</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>2,200円</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="T7" s="7" t="inlineStr">
+        <is>
+          <t>公式オンラインショップで在庫あり</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/hattansogenkei</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>今田酒造本店</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr"/>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>公式おすすめ・サタケ精米シリーズ</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>八反草 サタケシリーズ HENPEI</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>公開情報で判定材料不足</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr"/>
+      <c r="K8" s="9" t="inlineStr"/>
+      <c r="L8" s="9" t="inlineStr"/>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>冷酒</t>
+        </is>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>出典記載</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/hattansohenpei</t>
+        </is>
+      </c>
+      <c r="P8" s="9" t="inlineStr">
+        <is>
+          <t>広島県安芸高田市産八反草（契約栽培） 精米歩合 麹米 : 50% 掛米 : 60% 扁平精米 アルコール分 15％ 酵母 広島県酵母 酒母 速醸 仕様 直汲み</t>
+        </is>
+      </c>
+      <c r="Q8" s="9" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="R8" s="9" t="inlineStr">
+        <is>
+          <t>2,200円</t>
+        </is>
+      </c>
+      <c r="S8" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="T8" s="9" t="inlineStr">
+        <is>
+          <t>公式オンラインショップで在庫あり</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/hattansohenpei</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>今田酒造本店</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>八反草 純米 ハイブリッド生酛 特別栽培米R3</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>公開情報で判定材料不足</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr"/>
+      <c r="K9" s="7" t="inlineStr"/>
+      <c r="L9" s="7" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温 / 燗酒</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>出典記載</t>
+        </is>
+      </c>
+      <c r="O9" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/hybridkimoto-r3-2021by</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>は唯一富久長が育てる広島在来品種の八反草</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="R9" s="7" t="inlineStr">
+        <is>
+          <t>2,420円</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="T9" s="7" t="inlineStr">
+        <is>
+          <t>公式オンラインショップで在庫あり</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/hybridkimoto-r3-2021by</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>今田酒造本店</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr"/>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr"/>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>八反草 純米 ハイブリッド生酛 特別栽培米R4</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>公開情報で判定材料不足</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr"/>
+      <c r="K10" s="9" t="inlineStr"/>
+      <c r="L10" s="9" t="inlineStr"/>
+      <c r="M10" s="9" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温 / 燗酒</t>
+        </is>
+      </c>
+      <c r="N10" s="9" t="inlineStr">
+        <is>
+          <t>出典記載</t>
+        </is>
+      </c>
+      <c r="O10" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/hybridkimoto-r4-2022by</t>
+        </is>
+      </c>
+      <c r="P10" s="9" t="inlineStr">
+        <is>
+          <t>は唯一富久長が育てる広島在来品種の八反草</t>
+        </is>
+      </c>
+      <c r="Q10" s="9" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="R10" s="9" t="inlineStr">
+        <is>
+          <t>2,420円</t>
+        </is>
+      </c>
+      <c r="S10" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="T10" s="9" t="inlineStr">
+        <is>
+          <t>公式オンラインショップで在庫あり</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/hybridkimoto-r4-2022by</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>今田酒造本店</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr"/>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>八反草 純米 軟水仕込 辛口</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>辛口</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>商品名に辛口表記</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr"/>
+      <c r="K11" s="7" t="inlineStr"/>
+      <c r="L11" s="7" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>出典記載</t>
+        </is>
+      </c>
+      <c r="O11" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/hattansojunmai</t>
+        </is>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>広島県安芸高田市産八反草（契約栽培） 精米歩合 麹米 : 60% 掛米 : 65% 一部に真吟精米 アルコール分 14％ 酵母 広島県酵母 酒母 速醸 仕様 瓶</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="R11" s="7" t="inlineStr">
+        <is>
+          <t>1,980～3,520円</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="T11" s="7" t="inlineStr">
+        <is>
+          <t>公式オンラインショップで在庫あり</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/hattansojunmai</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>今田酒造本店</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr"/>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>公式が海風土シリーズを中心ラインとして訴求</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>海風土 Seafood 純米</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>公開情報で判定材料不足</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr"/>
+      <c r="K12" s="9" t="inlineStr"/>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>13度</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>冷酒 / 冷やして</t>
+        </is>
+      </c>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t>出典記載</t>
+        </is>
+      </c>
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/seafood</t>
+        </is>
+      </c>
+      <c r="P12" s="9" t="inlineStr">
+        <is>
+          <t>国産米 精米歩合 麹米 : 60% 掛米 : 70% アルコール分 13％ 酵母 広島県酵母 酒母 速醸 仕様 原酒 / 一回火入れ / 瓶貯蔵 おすすめ温度</t>
+        </is>
+      </c>
+      <c r="Q12" s="9" t="inlineStr">
+        <is>
+          <t>500ml / 720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="R12" s="9" t="inlineStr">
+        <is>
+          <t>1,870～3,850円</t>
+        </is>
+      </c>
+      <c r="S12" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="T12" s="9" t="inlineStr">
+        <is>
+          <t>公式オンラインショップで在庫あり</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/seafood</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>今田酒造本店</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr"/>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr"/>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>秋櫻〈コスモス〉 純米 ひやおろし</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>公開情報で判定材料不足</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr"/>
+      <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>出典記載</t>
+        </is>
+      </c>
+      <c r="O13" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/cosmos</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>広島県東広島市産山田錦 / 兵庫県特A地区山田錦 / 広島県産米 精米歩合 麹米 : 60% 掛米 : 60% アルコール分 15％ 酵母 広島県酵母 酒母 速</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="R13" s="7" t="inlineStr">
+        <is>
+          <t>1,870～3,850円</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>季節商品</t>
+        </is>
+      </c>
+      <c r="T13" s="7" t="inlineStr">
+        <is>
+          <t>公式オンラインショップで在庫あり / 二次DBでも存在確認</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/cosmos</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>今田酒造本店</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr"/>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>現行スパークリング主要商品</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>純米にごり スパークリング 白美 HAKUBI</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>公開情報で判定材料不足</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr"/>
+      <c r="K14" s="9" t="inlineStr"/>
+      <c r="L14" s="9" t="inlineStr"/>
+      <c r="M14" s="9" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温</t>
+        </is>
+      </c>
+      <c r="N14" s="9" t="inlineStr">
+        <is>
+          <t>出典記載</t>
+        </is>
+      </c>
+      <c r="O14" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/hakubi</t>
+        </is>
+      </c>
+      <c r="P14" s="9" t="inlineStr">
+        <is>
+          <t>広島県東広島市産山田錦 / 兵庫県特A地区山田錦 / 広島県産米 精米歩合 麹米 : 60% 掛米 : 65% アルコール分 14％ 酵母 広島県酵母 酒母 速</t>
+        </is>
+      </c>
+      <c r="Q14" s="9" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
+      <c r="R14" s="9" t="inlineStr">
+        <is>
+          <t>1,870円</t>
+        </is>
+      </c>
+      <c r="S14" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="T14" s="9" t="inlineStr">
+        <is>
+          <t>公式オンラインショップで在庫あり</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/hakubi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>今田酒造本店</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>公式現行定番</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>辛口純米</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>辛口</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>商品名に辛口表記</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr"/>
+      <c r="K15" s="7" t="inlineStr"/>
+      <c r="L15" s="7" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温 / 燗酒</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>出典記載</t>
+        </is>
+      </c>
+      <c r="O15" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/karakuchi</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>の一部に原形精米（真吟）のお米を使用しました</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="R15" s="7" t="inlineStr">
+        <is>
+          <t>1,980～3,300円</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="T15" s="7" t="inlineStr">
+        <is>
+          <t>公式オンラインショップで在庫あり / 二次DBでも存在確認</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/karakuchi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>今田酒造本店</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr"/>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>公式が唯一醸す八反草の中心ライン</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>八反草 純米吟醸</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>公開情報で判定材料不足</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr"/>
+      <c r="K16" s="9" t="inlineStr"/>
+      <c r="L16" s="9" t="inlineStr"/>
+      <c r="M16" s="9" t="inlineStr">
+        <is>
+          <t>冷酒</t>
+        </is>
+      </c>
+      <c r="N16" s="9" t="inlineStr">
+        <is>
+          <t>出典記載</t>
+        </is>
+      </c>
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/hattanso-junmaiginjo</t>
+        </is>
+      </c>
+      <c r="P16" s="9" t="inlineStr">
+        <is>
+          <t>広島県安芸高田市産八反草（契約栽培） 精米歩合 麹米 : 50% 掛米 : 60% アルコール分 15％ 酵母 広島県酵母 酒母 速醸 仕様 直汲み / 原酒</t>
+        </is>
+      </c>
+      <c r="Q16" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="R16" s="9" t="inlineStr">
+        <is>
+          <t>2,200～4,290円</t>
+        </is>
+      </c>
+      <c r="S16" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="T16" s="9" t="inlineStr">
+        <is>
+          <t>公式オンラインショップで在庫あり / 二次DBでも存在確認</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/hattanso-junmaiginjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>今田酒造本店</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>公式が唯一醸す八反草の中心ライン</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>八反草 純米吟醸 ハイブリッド生酛</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>公開情報で判定材料不足</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr"/>
+      <c r="K17" s="7" t="inlineStr"/>
+      <c r="L17" s="7" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>出典記載</t>
+        </is>
+      </c>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/hybridkimoto-junmaiginjo</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>広島県安芸高田市産八反草（契約栽培） 精米歩合 麹米 : 50% 掛米 : 60% アルコール分 15％ 酵母 広島県酵母 酒母 ハイブリッド生酛 仕様 原酒</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="R17" s="7" t="inlineStr">
+        <is>
+          <t>2,200～4,290円</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="T17" s="7" t="inlineStr">
+        <is>
+          <t>公式オンラインショップで在庫あり</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/hybridkimoto-junmaiginjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>今田酒造本店</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr"/>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr"/>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>山田錦 純米吟醸</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>公開情報で判定材料不足</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr"/>
+      <c r="K18" s="9" t="inlineStr"/>
+      <c r="L18" s="9" t="inlineStr"/>
+      <c r="M18" s="9" t="inlineStr">
+        <is>
+          <t>冷酒</t>
+        </is>
+      </c>
+      <c r="N18" s="9" t="inlineStr">
+        <is>
+          <t>出典記載</t>
+        </is>
+      </c>
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/yamadanishiki-junmaiginjo</t>
+        </is>
+      </c>
+      <c r="P18" s="9" t="inlineStr">
+        <is>
+          <t>広島県東広島市産山田錦 / 兵庫県特A地区山田錦 精米歩合 麹米 : 50% 掛米 : 60% アルコール分 16％ 酵母 広島県酵母のブレンド 酒母 速醸 仕</t>
+        </is>
+      </c>
+      <c r="Q18" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="R18" s="9" t="inlineStr">
+        <is>
+          <t>2,200～4,290円</t>
+        </is>
+      </c>
+      <c r="S18" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="T18" s="9" t="inlineStr">
+        <is>
+          <t>公式オンラインショップで在庫あり / 二次DBでも存在確認</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/yamadanishiki-junmaiginjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>今田酒造本店</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr"/>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr"/>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>秋櫻〈コスモス〉 純米吟醸 ひやおろし</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>公開情報で判定材料不足</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr"/>
+      <c r="K19" s="7" t="inlineStr"/>
+      <c r="L19" s="7" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>冷酒</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>出典記載</t>
+        </is>
+      </c>
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/cosmos-junmaiginjo</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>広島県東広島市産山田錦 / 兵庫県特A地区山田錦 / 広島県産米 精米歩合 麹米 : 50% 掛米 : 60% アルコール分 15％ 酵母 広島県酵母 酒母 速</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="R19" s="7" t="inlineStr">
+        <is>
+          <t>1,870～3,850円</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>季節商品</t>
+        </is>
+      </c>
+      <c r="T19" s="7" t="inlineStr">
+        <is>
+          <t>公式オンラインショップで在庫あり / 二次DBでも存在確認</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/cosmos-junmaiginjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>今田酒造本店</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr"/>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>公式現行主要商品</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸 美穂 Biho</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>公開情報で判定材料不足</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr"/>
+      <c r="K20" s="9" t="inlineStr"/>
+      <c r="L20" s="9" t="inlineStr"/>
+      <c r="M20" s="9" t="inlineStr">
+        <is>
+          <t>冷酒</t>
+        </is>
+      </c>
+      <c r="N20" s="9" t="inlineStr">
+        <is>
+          <t>出典記載</t>
+        </is>
+      </c>
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/biho</t>
+        </is>
+      </c>
+      <c r="P20" s="9" t="inlineStr">
+        <is>
+          <t>広島県東広島市産山田錦 / 兵庫県特A地区山田錦 / 広島県産米 精米歩合 麹米 : 50% 掛米 : 60% アルコール分 15％ 酵母 広島県酵母 酒母 速</t>
+        </is>
+      </c>
+      <c r="Q20" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="R20" s="9" t="inlineStr">
+        <is>
+          <t>2,090～3,960円</t>
+        </is>
+      </c>
+      <c r="S20" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="T20" s="9" t="inlineStr">
+        <is>
+          <t>公式オンラインショップで在庫あり</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/biho</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>今田酒造本店</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr"/>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>公式トップおすすめ商品に掲載する八反草上位酒</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>八反草 純米大吟醸</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>公開情報で判定材料不足</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr"/>
+      <c r="K21" s="7" t="inlineStr"/>
+      <c r="L21" s="7" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>冷酒</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>出典記載</t>
+        </is>
+      </c>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/daiginjo</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>は種もみから復活させた広島最古の酒米の在来品種、八反草を減農薬、減肥料で育てました</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="R21" s="7" t="inlineStr">
+        <is>
+          <t>2,200～13,200円</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="T21" s="7" t="inlineStr">
+        <is>
+          <t>公式オンラインショップで在庫あり</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/daiginjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>今田酒造本店</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr"/>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr"/>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>八反草 純米大吟醸 はしり</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>公開情報で判定材料不足</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr"/>
+      <c r="K22" s="9" t="inlineStr"/>
+      <c r="L22" s="9" t="inlineStr"/>
+      <c r="M22" s="9" t="inlineStr">
+        <is>
+          <t>冷酒</t>
+        </is>
+      </c>
+      <c r="N22" s="9" t="inlineStr">
+        <is>
+          <t>出典記載</t>
+        </is>
+      </c>
+      <c r="O22" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/daiginjo_hashiri</t>
+        </is>
+      </c>
+      <c r="P22" s="9" t="inlineStr">
+        <is>
+          <t>は種もみから復活させた広島最古の酒米の在来品種、八反草を減農薬、減肥料で育てました</t>
+        </is>
+      </c>
+      <c r="Q22" s="9" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="R22" s="9" t="inlineStr">
+        <is>
+          <t>6,600円</t>
+        </is>
+      </c>
+      <c r="S22" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="T22" s="9" t="inlineStr">
+        <is>
+          <t>公式オンラインショップで在庫あり</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/daiginjo_hashiri</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>今田酒造本店</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr"/>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>公式トップおすすめ商品に掲載する八反草上位酒</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>八反草 純米大吟醸 妙花風</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>公開情報で判定材料不足</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr"/>
+      <c r="K23" s="7" t="inlineStr"/>
+      <c r="L23" s="7" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>冷酒</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>出典記載</t>
+        </is>
+      </c>
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/daiginjo_myokafu</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>は種もみから復活させた広島最古の酒米の在来品種、八反草を減農薬、減肥料で育てました</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="R23" s="7" t="inlineStr">
+        <is>
+          <t>13,200円</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="T23" s="7" t="inlineStr">
+        <is>
+          <t>公式オンラインショップで在庫あり</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/daiginjo_myokafu</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>柄酒造</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>9代目於多福</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr"/>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr"/>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>9代目於多福 protos. 火入れ</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>公開情報で判定材料不足</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr"/>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>７１%</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="inlineStr">
+        <is>
+          <t>１３度</t>
+        </is>
+      </c>
+      <c r="M24" s="9" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温</t>
+        </is>
+      </c>
+      <c r="N24" s="9" t="inlineStr">
+        <is>
+          <t>現行酒販店商品情報</t>
+        </is>
+      </c>
+      <c r="O24" s="8" t="inlineStr">
+        <is>
+          <t>https://tawawasake.base.shop/items/134292512</t>
+        </is>
+      </c>
+      <c r="P24" s="9" t="inlineStr">
+        <is>
+          <t>八反錦 精米歩合：７１% アルコール度数：１３度 酵母：協会７号 もろみ日数：41日 (71、13、7、41、全て素数です） {"id":91895203104</t>
+        </is>
+      </c>
+      <c r="Q24" s="9" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="R24" s="9" t="inlineStr">
+        <is>
+          <t>1,980円</t>
+        </is>
+      </c>
+      <c r="S24" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="T24" s="9" t="inlineStr">
+        <is>
+          <t>公式オンラインショップで販売確認</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/products/9代目於多福-protos-720ml-火入れ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>柄酒造</t>
+        </is>
+      </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
+          <t>9代目於多福</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr"/>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr"/>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
           <t>9代目於多福 つきあかり</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>公開情報で判定材料不足</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr"/>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr"/>
+      <c r="K25" s="7" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>15度</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr">
         <is>
           <t>冷酒 / 常温</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr">
+      <c r="N25" s="7" t="inlineStr">
         <is>
           <t>出典記載</t>
         </is>
       </c>
-      <c r="K25" s="8" t="inlineStr">
+      <c r="O25" s="8" t="inlineStr">
         <is>
           <t>https://www.tsukasyuzou.jp/products/9代目於多福-つきあかり-720ml</t>
         </is>
       </c>
-      <c r="L25" s="7" t="inlineStr">
+      <c r="P25" s="7" t="inlineStr">
         <is>
           <t>山田錦 精米歩合：60% アルコール度数：15度 飲み方：◎冷酒 ○常温 {"id":8046672674990,"title":"9代目於多福 つきあかり 7</t>
         </is>
       </c>
-      <c r="M25" s="7" t="inlineStr">
+      <c r="Q25" s="7" t="inlineStr">
         <is>
           <t>720ml</t>
         </is>
       </c>
-      <c r="N25" s="7" t="inlineStr">
+      <c r="R25" s="7" t="inlineStr">
         <is>
           <t>2,090円</t>
         </is>
       </c>
-      <c r="O25" s="7" t="inlineStr">
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="P25" s="7" t="inlineStr">
+      <c r="T25" s="7" t="inlineStr">
         <is>
           <t>公式オンラインショップで販売確認</t>
         </is>
       </c>
-      <c r="Q25" s="8" t="inlineStr">
+      <c r="U25" s="8" t="inlineStr">
         <is>
           <t>https://www.tsukasyuzou.jp/products/9代目於多福-つきあかり-720ml</t>
         </is>
@@ -2405,76 +5046,92 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
+          <t>於多福</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr"/>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>従来ブランド高級ライン</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
           <t>於多福 一番取り</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>公開情報で判定材料不足</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr"/>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="J26" s="9" t="inlineStr"/>
+      <c r="K26" s="9" t="inlineStr">
         <is>
           <t>40％</t>
         </is>
       </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="L26" s="9" t="inlineStr">
         <is>
           <t>16.5度</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="M26" s="9" t="inlineStr">
         <is>
           <t>冷酒</t>
         </is>
       </c>
-      <c r="J26" s="9" t="inlineStr">
+      <c r="N26" s="9" t="inlineStr">
         <is>
           <t>出典記載</t>
         </is>
       </c>
-      <c r="K26" s="8" t="inlineStr">
+      <c r="O26" s="8" t="inlineStr">
         <is>
           <t>https://www.tsukasyuzou.jp/products/関西一-一番取り-720ml</t>
         </is>
       </c>
-      <c r="L26" s="9" t="inlineStr">
+      <c r="P26" s="9" t="inlineStr">
         <is>
           <t>千本錦 精米歩合：40％ アルコール度数：16.5度 飲み方：◎冷酒 {"id":7986565415086,"title":"於多福 一番取り 720ml（桐</t>
         </is>
       </c>
-      <c r="M26" s="9" t="inlineStr">
+      <c r="Q26" s="9" t="inlineStr">
         <is>
           <t>720ml</t>
         </is>
       </c>
-      <c r="N26" s="9" t="inlineStr">
+      <c r="R26" s="9" t="inlineStr">
         <is>
           <t>6,600円</t>
         </is>
       </c>
-      <c r="O26" s="9" t="inlineStr">
+      <c r="S26" s="9" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="P26" s="9" t="inlineStr">
+      <c r="T26" s="9" t="inlineStr">
         <is>
           <t>公式オンラインショップで販売確認</t>
         </is>
       </c>
-      <c r="Q26" s="8" t="inlineStr">
+      <c r="U26" s="8" t="inlineStr">
         <is>
           <t>https://www.tsukasyuzou.jp/products/関西一-一番取り-720ml</t>
         </is>
@@ -2488,76 +5145,92 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
+          <t>於多福</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr"/>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>従来主ブランドの上位定番</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
           <t>於多福 大吟醸</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>大吟醸</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>公開情報で判定材料不足</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr"/>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr"/>
+      <c r="K27" s="7" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="L27" s="7" t="inlineStr">
         <is>
           <t>16.5度</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr">
         <is>
           <t>冷酒 / 常温</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="N27" s="7" t="inlineStr">
         <is>
           <t>出典記載</t>
         </is>
       </c>
-      <c r="K27" s="8" t="inlineStr">
+      <c r="O27" s="8" t="inlineStr">
         <is>
           <t>https://www.tsukasyuzou.jp/products/於多福-大吟醸-1800ml</t>
         </is>
       </c>
-      <c r="L27" s="7" t="inlineStr">
+      <c r="P27" s="7" t="inlineStr">
         <is>
           <t>千本錦 精米歩合：40% アルコール度数：16.5度 飲み方：◎冷酒 〇常温 「関西一 大吟醸 1800ml」という名称で親しまれてきましたが、2023年5月よ</t>
         </is>
       </c>
-      <c r="M27" s="7" t="inlineStr">
+      <c r="Q27" s="7" t="inlineStr">
         <is>
           <t>720ml / 1,800ml</t>
         </is>
       </c>
-      <c r="N27" s="7" t="inlineStr">
+      <c r="R27" s="7" t="inlineStr">
         <is>
           <t>3,080～6,160円</t>
         </is>
       </c>
-      <c r="O27" s="7" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="P27" s="7" t="inlineStr">
+      <c r="T27" s="7" t="inlineStr">
         <is>
           <t>公式オンラインショップで販売確認 / 二次DBでも存在確認</t>
         </is>
       </c>
-      <c r="Q27" s="8" t="inlineStr">
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>https://www.tsukasyuzou.jp/products/於多福-大吟醸-1800ml</t>
         </is>
@@ -2571,76 +5244,88 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
+          <t>於多福</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr"/>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr"/>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
           <t>於多福 本醸造</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="G28" s="9" t="inlineStr">
         <is>
           <t>本醸造</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="H28" s="9" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="I28" s="9" t="inlineStr">
         <is>
           <t>公開情報で判定材料不足</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr"/>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="J28" s="9" t="inlineStr"/>
+      <c r="K28" s="9" t="inlineStr">
         <is>
           <t>65％</t>
         </is>
       </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="L28" s="9" t="inlineStr">
         <is>
           <t>15.5度</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
+      <c r="M28" s="9" t="inlineStr">
         <is>
           <t>冷酒 / 常温 / 熱燗</t>
         </is>
       </c>
-      <c r="J28" s="9" t="inlineStr">
+      <c r="N28" s="9" t="inlineStr">
         <is>
           <t>出典記載</t>
         </is>
       </c>
-      <c r="K28" s="8" t="inlineStr">
+      <c r="O28" s="8" t="inlineStr">
         <is>
           <t>https://www.tsukasyuzou.jp/products/関西一-本醸造-720ml</t>
         </is>
       </c>
-      <c r="L28" s="9" t="inlineStr">
+      <c r="P28" s="9" t="inlineStr">
         <is>
           <t>八反錦 精米歩合：65％ アルコール度数：15.5度 飲み方：◎冷酒 ◎常温 ◎熱燗 {"id":7986570035374,"title":"於多福 本醸造</t>
         </is>
       </c>
-      <c r="M28" s="9" t="inlineStr">
+      <c r="Q28" s="9" t="inlineStr">
         <is>
           <t>720ml</t>
         </is>
       </c>
-      <c r="N28" s="9" t="inlineStr">
+      <c r="R28" s="9" t="inlineStr">
         <is>
           <t>1,320円</t>
         </is>
       </c>
-      <c r="O28" s="9" t="inlineStr">
+      <c r="S28" s="9" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="P28" s="9" t="inlineStr">
+      <c r="T28" s="9" t="inlineStr">
         <is>
           <t>公式オンラインショップで販売確認</t>
         </is>
       </c>
-      <c r="Q28" s="8" t="inlineStr">
+      <c r="U28" s="8" t="inlineStr">
         <is>
           <t>https://www.tsukasyuzou.jp/products/関西一-本醸造-720ml</t>
         </is>
@@ -2654,72 +5339,88 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
+          <t>9代目於多福</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr"/>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>現行中心シリーズ</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
           <t>9代目於多福 特別純米 火入れ</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>特別純米</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>公開情報で判定材料不足</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr"/>
-      <c r="G29" s="7" t="inlineStr"/>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr"/>
+      <c r="K29" s="7" t="inlineStr"/>
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>15度</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr">
         <is>
           <t>冷酒 / 常温</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="N29" s="7" t="inlineStr">
         <is>
           <t>出典記載</t>
         </is>
       </c>
-      <c r="K29" s="8" t="inlineStr">
+      <c r="O29" s="8" t="inlineStr">
         <is>
           <t>https://www.tsukasyuzou.jp/products/火入れ-9代目於多福-特別純米</t>
         </is>
       </c>
-      <c r="L29" s="7" t="inlineStr">
+      <c r="P29" s="7" t="inlineStr">
         <is>
           <t>八反錦 精米歩合：米麹 50% 掛け米 60% アルコール度数：15度 飲み方：◎冷酒 ○常温 {"id":7981920288942,"title":"【火入</t>
         </is>
       </c>
-      <c r="M29" s="7" t="inlineStr">
+      <c r="Q29" s="7" t="inlineStr">
         <is>
           <t>720ml</t>
         </is>
       </c>
-      <c r="N29" s="7" t="inlineStr">
+      <c r="R29" s="7" t="inlineStr">
         <is>
           <t>1,980円</t>
         </is>
       </c>
-      <c r="O29" s="7" t="inlineStr">
+      <c r="S29" s="7" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="P29" s="7" t="inlineStr">
+      <c r="T29" s="7" t="inlineStr">
         <is>
           <t>公式オンラインショップで販売確認</t>
         </is>
       </c>
-      <c r="Q29" s="8" t="inlineStr">
+      <c r="U29" s="8" t="inlineStr">
         <is>
           <t>https://www.tsukasyuzou.jp/products/火入れ-9代目於多福-特別純米</t>
         </is>
@@ -2733,76 +5434,92 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
+          <t>9代目於多福</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr"/>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>現行中心シリーズ</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
           <t>9代目於多福 純米 火入れ</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="G30" s="9" t="inlineStr">
         <is>
           <t>純米</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="H30" s="9" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="I30" s="9" t="inlineStr">
         <is>
           <t>公開情報で判定材料不足</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr"/>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="J30" s="9" t="inlineStr"/>
+      <c r="K30" s="9" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="L30" s="9" t="inlineStr">
         <is>
           <t>15度</t>
         </is>
       </c>
-      <c r="I30" s="9" t="inlineStr">
+      <c r="M30" s="9" t="inlineStr">
         <is>
           <t>冷酒 / 常温</t>
         </is>
       </c>
-      <c r="J30" s="9" t="inlineStr">
+      <c r="N30" s="9" t="inlineStr">
         <is>
           <t>出典記載</t>
         </is>
       </c>
-      <c r="K30" s="8" t="inlineStr">
+      <c r="O30" s="8" t="inlineStr">
         <is>
           <t>https://www.tsukasyuzou.jp/products/火入れ-9代目於多福-純米</t>
         </is>
       </c>
-      <c r="L30" s="9" t="inlineStr">
+      <c r="P30" s="9" t="inlineStr">
         <is>
           <t>八反錦 精米歩合：60% アルコール度数：15度 飲み方：◎冷酒 ○常温 {"id":7981013172398,"title":"【火入れ】9代目於多福 純米</t>
         </is>
       </c>
-      <c r="M30" s="9" t="inlineStr">
+      <c r="Q30" s="9" t="inlineStr">
         <is>
           <t>720ml / 1,800ml</t>
         </is>
       </c>
-      <c r="N30" s="9" t="inlineStr">
+      <c r="R30" s="9" t="inlineStr">
         <is>
           <t>1,760～3,300円</t>
         </is>
       </c>
-      <c r="O30" s="9" t="inlineStr">
+      <c r="S30" s="9" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="P30" s="9" t="inlineStr">
+      <c r="T30" s="9" t="inlineStr">
         <is>
           <t>公式オンラインショップで販売確認</t>
         </is>
       </c>
-      <c r="Q30" s="8" t="inlineStr">
+      <c r="U30" s="8" t="inlineStr">
         <is>
           <t>https://www.tsukasyuzou.jp/products/火入れ-9代目於多福-純米</t>
         </is>
@@ -2816,76 +5533,92 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
+          <t>於多福</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr"/>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>現行中心シリーズの上位酒</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
           <t>於多福 純米</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>純米</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>公開情報で判定材料不足</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr"/>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr"/>
+      <c r="K31" s="7" t="inlineStr">
         <is>
           <t>60％</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>15.5度</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="M31" s="7" t="inlineStr">
         <is>
           <t>冷酒 / 常温 / 熱燗</t>
         </is>
       </c>
-      <c r="J31" s="7" t="inlineStr">
+      <c r="N31" s="7" t="inlineStr">
         <is>
           <t>出典記載</t>
         </is>
       </c>
-      <c r="K31" s="8" t="inlineStr">
+      <c r="O31" s="8" t="inlineStr">
         <is>
           <t>https://www.tsukasyuzou.jp/products/於多福-純米-1800ml</t>
         </is>
       </c>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="P31" s="7" t="inlineStr">
         <is>
           <t>八反錦 アルコール度数：15.5度 飲み方：〇冷酒 ◎常温 ◎熱燗 {"id":7986568560814,"title":"於多福 純米 1800ml","h</t>
         </is>
       </c>
-      <c r="M31" s="7" t="inlineStr">
+      <c r="Q31" s="7" t="inlineStr">
         <is>
           <t>720ml / 1,800ml</t>
         </is>
       </c>
-      <c r="N31" s="7" t="inlineStr">
+      <c r="R31" s="7" t="inlineStr">
         <is>
           <t>1,760～3,740円</t>
         </is>
       </c>
-      <c r="O31" s="7" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="P31" s="7" t="inlineStr">
+      <c r="T31" s="7" t="inlineStr">
         <is>
           <t>公式オンラインショップで販売確認 / 二次DBでも存在確認</t>
         </is>
       </c>
-      <c r="Q31" s="8" t="inlineStr">
+      <c r="U31" s="8" t="inlineStr">
         <is>
           <t>https://www.tsukasyuzou.jp/products/於多福-純米-1800ml</t>
         </is>
@@ -2899,76 +5632,92 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
+          <t>9代目於多福</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr"/>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>現行中心シリーズ</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
           <t>9代目於多福 純米吟醸 すずかぜ</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="G32" s="9" t="inlineStr">
         <is>
           <t>純米吟醸</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="H32" s="9" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="I32" s="9" t="inlineStr">
         <is>
           <t>公開情報で判定材料不足</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr"/>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="J32" s="9" t="inlineStr"/>
+      <c r="K32" s="9" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="H32" s="9" t="inlineStr">
+      <c r="L32" s="9" t="inlineStr">
         <is>
           <t>15度</t>
         </is>
       </c>
-      <c r="I32" s="9" t="inlineStr">
+      <c r="M32" s="9" t="inlineStr">
         <is>
           <t>冷酒 / 常温 / ロック</t>
         </is>
       </c>
-      <c r="J32" s="9" t="inlineStr">
+      <c r="N32" s="9" t="inlineStr">
         <is>
           <t>出典記載</t>
         </is>
       </c>
-      <c r="K32" s="8" t="inlineStr">
+      <c r="O32" s="8" t="inlineStr">
         <is>
           <t>https://www.tsukasyuzou.jp/products/9代目於多福-すずかぜ-720ml</t>
         </is>
       </c>
-      <c r="L32" s="9" t="inlineStr">
+      <c r="P32" s="9" t="inlineStr">
         <is>
           <t>雄町 精米歩合：50% アルコール度数：15度 飲み方：◎冷酒 ○常温 {"id":8008537899182,"title":"9代目於多福 純米吟醸 すずか</t>
         </is>
       </c>
-      <c r="M32" s="9" t="inlineStr">
+      <c r="Q32" s="9" t="inlineStr">
         <is>
           <t>720ml / 1,800ml</t>
         </is>
       </c>
-      <c r="N32" s="9" t="inlineStr">
+      <c r="R32" s="9" t="inlineStr">
         <is>
           <t>1,760～3,740円</t>
         </is>
       </c>
-      <c r="O32" s="9" t="inlineStr">
+      <c r="S32" s="9" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="P32" s="9" t="inlineStr">
+      <c r="T32" s="9" t="inlineStr">
         <is>
           <t>公式オンラインショップで販売確認</t>
         </is>
       </c>
-      <c r="Q32" s="8" t="inlineStr">
+      <c r="U32" s="8" t="inlineStr">
         <is>
           <t>https://www.tsukasyuzou.jp/products/9代目於多福-すずかぜ-720ml</t>
         </is>
@@ -2982,76 +5731,92 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
+          <t>9代目於多福</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr"/>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>現行中心シリーズ</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
           <t>9代目於多福 純米吟醸 火入れ</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>純米吟醸</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>公開情報で判定材料不足</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr"/>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr"/>
+      <c r="K33" s="7" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>15度</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="M33" s="7" t="inlineStr">
         <is>
           <t>冷酒 / 常温</t>
         </is>
       </c>
-      <c r="J33" s="7" t="inlineStr">
+      <c r="N33" s="7" t="inlineStr">
         <is>
           <t>出典記載</t>
         </is>
       </c>
-      <c r="K33" s="8" t="inlineStr">
+      <c r="O33" s="8" t="inlineStr">
         <is>
           <t>https://www.tsukasyuzou.jp/products/火入れ-9代目於多福-純米吟醸</t>
         </is>
       </c>
-      <c r="L33" s="7" t="inlineStr">
+      <c r="P33" s="7" t="inlineStr">
         <is>
           <t>八反錦 精米歩合：50% アルコール度数：15度 飲み方：◎冷酒 〇常温 {"id":7981919305902,"title":"【火入れ】9代目於多福 純米</t>
         </is>
       </c>
-      <c r="M33" s="7" t="inlineStr">
+      <c r="Q33" s="7" t="inlineStr">
         <is>
           <t>720ml / 1,800ml</t>
         </is>
       </c>
-      <c r="N33" s="7" t="inlineStr">
+      <c r="R33" s="7" t="inlineStr">
         <is>
           <t>1,760～3,740円</t>
         </is>
       </c>
-      <c r="O33" s="7" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="P33" s="7" t="inlineStr">
+      <c r="T33" s="7" t="inlineStr">
         <is>
           <t>公式オンラインショップで販売確認</t>
         </is>
       </c>
-      <c r="Q33" s="8" t="inlineStr">
+      <c r="U33" s="8" t="inlineStr">
         <is>
           <t>https://www.tsukasyuzou.jp/products/火入れ-9代目於多福-純米吟醸</t>
         </is>
@@ -3065,76 +5830,92 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
+          <t>於多福</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr"/>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>従来主ブランドの主要商品</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
           <t>於多福 純米吟醸</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="G34" s="9" t="inlineStr">
         <is>
           <t>純米吟醸</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="H34" s="9" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="I34" s="9" t="inlineStr">
         <is>
           <t>公開情報で判定材料不足</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr"/>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="J34" s="9" t="inlineStr"/>
+      <c r="K34" s="9" t="inlineStr">
         <is>
           <t>60％</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="L34" s="9" t="inlineStr">
         <is>
           <t>15.5度</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
+      <c r="M34" s="9" t="inlineStr">
         <is>
           <t>冷酒 / 冷やして / 常温</t>
         </is>
       </c>
-      <c r="J34" s="9" t="inlineStr">
+      <c r="N34" s="9" t="inlineStr">
         <is>
           <t>出典記載</t>
         </is>
       </c>
-      <c r="K34" s="8" t="inlineStr">
+      <c r="O34" s="8" t="inlineStr">
         <is>
           <t>https://www.tsukasyuzou.jp/products/於多福-純米吟醸-1800ml</t>
         </is>
       </c>
-      <c r="L34" s="9" t="inlineStr">
+      <c r="P34" s="9" t="inlineStr">
         <is>
           <t>八反錦 精米歩合：60％ アルコール度数：15.5度 飲み方：◎冷酒 ◎常温 {"id":7986567381166,"title":"於多福 純米吟醸 180</t>
         </is>
       </c>
-      <c r="M34" s="9" t="inlineStr">
+      <c r="Q34" s="9" t="inlineStr">
         <is>
           <t>720ml / 1,800ml</t>
         </is>
       </c>
-      <c r="N34" s="9" t="inlineStr">
+      <c r="R34" s="9" t="inlineStr">
         <is>
           <t>1,760～3,740円</t>
         </is>
       </c>
-      <c r="O34" s="9" t="inlineStr">
+      <c r="S34" s="9" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="P34" s="9" t="inlineStr">
+      <c r="T34" s="9" t="inlineStr">
         <is>
           <t>公式オンラインショップで販売確認 / 二次DBでも存在確認</t>
         </is>
       </c>
-      <c r="Q34" s="8" t="inlineStr">
+      <c r="U34" s="8" t="inlineStr">
         <is>
           <t>https://www.tsukasyuzou.jp/products/於多福-純米吟醸-1800ml</t>
         </is>
@@ -3148,76 +5929,92 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
+          <t>9代目於多福</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr"/>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>現行中心シリーズの上位酒</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
           <t>9代目於多福 純米大吟醸 火入れ</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>純米大吟醸</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>公開情報で判定材料不足</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr"/>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr"/>
+      <c r="K35" s="7" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>15度</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="M35" s="7" t="inlineStr">
         <is>
           <t>冷酒 / 常温</t>
         </is>
       </c>
-      <c r="J35" s="7" t="inlineStr">
+      <c r="N35" s="7" t="inlineStr">
         <is>
           <t>出典記載</t>
         </is>
       </c>
-      <c r="K35" s="8" t="inlineStr">
+      <c r="O35" s="8" t="inlineStr">
         <is>
           <t>https://www.tsukasyuzou.jp/products/火入れ-9代目於多福-純米大吟醸-720ml-1800ml</t>
         </is>
       </c>
-      <c r="L35" s="7" t="inlineStr">
+      <c r="P35" s="7" t="inlineStr">
         <is>
           <t>千本錦 精米歩合：40% アルコール度数：15度 飲み方：◎冷酒 ○常温 {"id":8053542846638,"title":"【火入れ】9代目於多福 純米</t>
         </is>
       </c>
-      <c r="M35" s="7" t="inlineStr">
+      <c r="Q35" s="7" t="inlineStr">
         <is>
           <t>720ml / 1,800ml</t>
         </is>
       </c>
-      <c r="N35" s="7" t="inlineStr">
+      <c r="R35" s="7" t="inlineStr">
         <is>
           <t>1,760～3,300円</t>
         </is>
       </c>
-      <c r="O35" s="7" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="P35" s="7" t="inlineStr">
+      <c r="T35" s="7" t="inlineStr">
         <is>
           <t>公式オンラインショップで販売確認</t>
         </is>
       </c>
-      <c r="Q35" s="8" t="inlineStr">
+      <c r="U35" s="8" t="inlineStr">
         <is>
           <t>https://www.tsukasyuzou.jp/products/火入れ-9代目於多福-純米大吟醸-720ml-1800ml</t>
         </is>
@@ -3231,68 +6028,82 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
+          <t>賀茂金秀</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr"/>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>公式通年・「入魂の逸品」</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
           <t>賀茂金秀 特別純米</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="G36" s="9" t="inlineStr">
         <is>
           <t>特別純米</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="H36" s="9" t="inlineStr">
         <is>
           <t>やや辛口</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="I36" s="9" t="inlineStr">
         <is>
           <t>日本酒度からの目安</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
-      <c r="G36" s="9" t="inlineStr"/>
-      <c r="H36" s="9" t="inlineStr"/>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>冷酒 / 燗酒（45～50℃）</t>
-        </is>
-      </c>
-      <c r="J36" s="9" t="inlineStr">
-        <is>
-          <t>現行酒販店商品情報</t>
-        </is>
-      </c>
-      <c r="K36" s="8" t="inlineStr">
-        <is>
-          <t>https://reika-sake.com/products/34kmk01201121</t>
-        </is>
-      </c>
+      <c r="J36" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" s="9" t="inlineStr"/>
       <c r="L36" s="9" t="inlineStr"/>
       <c r="M36" s="9" t="inlineStr">
         <is>
+          <t>冷酒 / 燗酒（45～50℃）</t>
+        </is>
+      </c>
+      <c r="N36" s="9" t="inlineStr">
+        <is>
+          <t>現行酒販店商品情報</t>
+        </is>
+      </c>
+      <c r="O36" s="8" t="inlineStr">
+        <is>
+          <t>https://reika-sake.com/products/34kmk01201121</t>
+        </is>
+      </c>
+      <c r="P36" s="9" t="inlineStr"/>
+      <c r="Q36" s="9" t="inlineStr">
+        <is>
           <t>720ml / 1,800ml</t>
         </is>
       </c>
-      <c r="N36" s="9" t="inlineStr">
+      <c r="R36" s="9" t="inlineStr">
         <is>
           <t>1,870～3,476円</t>
         </is>
       </c>
-      <c r="O36" s="9" t="inlineStr">
+      <c r="S36" s="9" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="P36" s="9" t="inlineStr">
+      <c r="T36" s="9" t="inlineStr">
         <is>
           <t>公式定番ラインナップ掲載 / 二次DBでも存在確認</t>
         </is>
       </c>
-      <c r="Q36" s="8" t="inlineStr">
+      <c r="U36" s="8" t="inlineStr">
         <is>
           <t>https://www.kamokin.com/line_up/regular.html</t>
         </is>
@@ -3306,68 +6117,82 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
+          <t>賀茂金秀</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr"/>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>公式通年低アルコール系</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
           <t>賀茂金秀 特別純米13</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>特別純米</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>中口</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>日本酒度からの目安</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>冷酒（5～15℃前後）</t>
-        </is>
-      </c>
-      <c r="J37" s="7" t="inlineStr">
-        <is>
-          <t>現行酒販店商品情報</t>
-        </is>
-      </c>
-      <c r="K37" s="8" t="inlineStr">
-        <is>
-          <t>https://reika-sake.com/products/34kmk01203121</t>
-        </is>
-      </c>
+      <c r="J37" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K37" s="7" t="inlineStr"/>
       <c r="L37" s="7" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr">
         <is>
+          <t>冷酒（5～15℃前後）</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="inlineStr">
+        <is>
+          <t>現行酒販店商品情報</t>
+        </is>
+      </c>
+      <c r="O37" s="8" t="inlineStr">
+        <is>
+          <t>https://reika-sake.com/products/34kmk01203121</t>
+        </is>
+      </c>
+      <c r="P37" s="7" t="inlineStr"/>
+      <c r="Q37" s="7" t="inlineStr">
+        <is>
           <t>720ml / 1,800ml</t>
         </is>
       </c>
-      <c r="N37" s="7" t="inlineStr">
+      <c r="R37" s="7" t="inlineStr">
         <is>
           <t>1,870～3,465円</t>
         </is>
       </c>
-      <c r="O37" s="7" t="inlineStr">
+      <c r="S37" s="7" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="P37" s="7" t="inlineStr">
+      <c r="T37" s="7" t="inlineStr">
         <is>
           <t>日本酒造組合中央会系JSP蔵元ページの代表商品</t>
         </is>
       </c>
-      <c r="Q37" s="8" t="inlineStr">
+      <c r="U37" s="8" t="inlineStr">
         <is>
           <t>https://j-s-p.or.jp/kuramoto/kanemitsu</t>
         </is>
@@ -3381,68 +6206,82 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
+          <t>賀茂金秀</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr"/>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>公式通年辛口ライン</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
           <t>賀茂金秀 辛口特別純米</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="G38" s="9" t="inlineStr">
         <is>
           <t>特別純米</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="H38" s="9" t="inlineStr">
         <is>
           <t>辛口</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="I38" s="9" t="inlineStr">
         <is>
           <t>商品名に辛口表記</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>+8</t>
-        </is>
-      </c>
-      <c r="G38" s="9" t="inlineStr"/>
-      <c r="H38" s="9" t="inlineStr"/>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>冷酒（10～15℃前後）</t>
-        </is>
-      </c>
-      <c r="J38" s="9" t="inlineStr">
-        <is>
-          <t>日本酒情報DB</t>
-        </is>
-      </c>
-      <c r="K38" s="8" t="inlineStr">
-        <is>
-          <t>https://www.sakenomy.jp/sake/TST0000010137/</t>
-        </is>
-      </c>
+      <c r="J38" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="K38" s="9" t="inlineStr"/>
       <c r="L38" s="9" t="inlineStr"/>
       <c r="M38" s="9" t="inlineStr">
         <is>
+          <t>冷酒（10～15℃前後）</t>
+        </is>
+      </c>
+      <c r="N38" s="9" t="inlineStr">
+        <is>
+          <t>日本酒情報DB</t>
+        </is>
+      </c>
+      <c r="O38" s="8" t="inlineStr">
+        <is>
+          <t>https://www.sakenomy.jp/sake/TST0000010137/</t>
+        </is>
+      </c>
+      <c r="P38" s="9" t="inlineStr"/>
+      <c r="Q38" s="9" t="inlineStr">
+        <is>
           <t>720ml / 1,800ml</t>
         </is>
       </c>
-      <c r="N38" s="9" t="inlineStr">
+      <c r="R38" s="9" t="inlineStr">
         <is>
           <t>1,870～3,465円</t>
         </is>
       </c>
-      <c r="O38" s="9" t="inlineStr">
+      <c r="S38" s="9" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="P38" s="9" t="inlineStr">
+      <c r="T38" s="9" t="inlineStr">
         <is>
           <t>公式定番ラインナップ掲載 / 二次DBでも存在確認</t>
         </is>
       </c>
-      <c r="Q38" s="8" t="inlineStr">
+      <c r="U38" s="8" t="inlineStr">
         <is>
           <t>https://www.kamokin.com/line_up/regular.html</t>
         </is>
@@ -3456,68 +6295,82 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
+          <t>賀茂金秀</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr"/>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>公式通年・食との相性を訴求する代表銘柄</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
           <t>賀茂金秀 純米吟醸 雄町</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>純米吟醸</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>やや辛口</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>日本酒度からの目安</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>+2</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr"/>
-      <c r="H39" s="7" t="inlineStr"/>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>冷酒（10～15℃前後）</t>
-        </is>
-      </c>
-      <c r="J39" s="7" t="inlineStr">
-        <is>
-          <t>日本酒情報DB</t>
-        </is>
-      </c>
-      <c r="K39" s="8" t="inlineStr">
-        <is>
-          <t>https://www.sakenomy.jp/sake/TST0000007478/</t>
-        </is>
-      </c>
+      <c r="J39" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K39" s="7" t="inlineStr"/>
       <c r="L39" s="7" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr">
         <is>
+          <t>冷酒（10～15℃前後）</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="inlineStr">
+        <is>
+          <t>日本酒情報DB</t>
+        </is>
+      </c>
+      <c r="O39" s="8" t="inlineStr">
+        <is>
+          <t>https://www.sakenomy.jp/sake/TST0000007478/</t>
+        </is>
+      </c>
+      <c r="P39" s="7" t="inlineStr"/>
+      <c r="Q39" s="7" t="inlineStr">
+        <is>
           <t>720ml / 1,800ml</t>
         </is>
       </c>
-      <c r="N39" s="7" t="inlineStr">
+      <c r="R39" s="7" t="inlineStr">
         <is>
           <t>2,200～3,960円</t>
         </is>
       </c>
-      <c r="O39" s="7" t="inlineStr">
+      <c r="S39" s="7" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="P39" s="7" t="inlineStr">
+      <c r="T39" s="7" t="inlineStr">
         <is>
           <t>公式定番ラインナップ掲載 / 日本酒造組合中央会系JSP蔵元ページの代表商品 / 二次DBでも存在確認</t>
         </is>
       </c>
-      <c r="Q39" s="8" t="inlineStr">
+      <c r="U39" s="8" t="inlineStr">
         <is>
           <t>https://www.kamokin.com/line_up/regular.html</t>
         </is>
@@ -3531,68 +6384,82 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
+          <t>賀茂金秀</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr"/>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>公式通年最高級ライン</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
           <t>賀茂金秀 純米大吟醸35</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="G40" s="9" t="inlineStr">
         <is>
           <t>純米大吟醸</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="H40" s="9" t="inlineStr">
         <is>
           <t>中口</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="I40" s="9" t="inlineStr">
         <is>
           <t>日本酒度からの目安</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="G40" s="9" t="inlineStr"/>
-      <c r="H40" s="9" t="inlineStr"/>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>冷酒（10～15℃前後）</t>
-        </is>
-      </c>
-      <c r="J40" s="9" t="inlineStr">
-        <is>
-          <t>日本酒情報DB</t>
-        </is>
-      </c>
-      <c r="K40" s="8" t="inlineStr">
-        <is>
-          <t>https://www.sakenomy.jp/sake/TST0000041706/</t>
-        </is>
-      </c>
+      <c r="J40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" s="9" t="inlineStr"/>
       <c r="L40" s="9" t="inlineStr"/>
       <c r="M40" s="9" t="inlineStr">
         <is>
+          <t>冷酒（10～15℃前後）</t>
+        </is>
+      </c>
+      <c r="N40" s="9" t="inlineStr">
+        <is>
+          <t>日本酒情報DB</t>
+        </is>
+      </c>
+      <c r="O40" s="8" t="inlineStr">
+        <is>
+          <t>https://www.sakenomy.jp/sake/TST0000041706/</t>
+        </is>
+      </c>
+      <c r="P40" s="9" t="inlineStr"/>
+      <c r="Q40" s="9" t="inlineStr">
+        <is>
           <t>720ml / 1,800ml</t>
         </is>
       </c>
-      <c r="N40" s="9" t="inlineStr">
+      <c r="R40" s="9" t="inlineStr">
         <is>
           <t>3,300～11,000円</t>
         </is>
       </c>
-      <c r="O40" s="9" t="inlineStr">
+      <c r="S40" s="9" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="P40" s="9" t="inlineStr">
+      <c r="T40" s="9" t="inlineStr">
         <is>
           <t>公式定番ラインナップ掲載 / 日本酒造組合中央会系JSP蔵元ページの代表商品</t>
         </is>
       </c>
-      <c r="Q40" s="8" t="inlineStr">
+      <c r="U40" s="8" t="inlineStr">
         <is>
           <t>https://www.kamokin.com/line_up/regular.html</t>
         </is>
@@ -3606,154 +6473,168 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
+          <t>賀茂金秀</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr"/>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>公式通年純米大吟醸</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
           <t>賀茂金秀 純米大吟醸40</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>純米大吟醸</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>中口</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>日本酒度からの目安</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="G41" s="7" t="inlineStr"/>
-      <c r="H41" s="7" t="inlineStr"/>
-      <c r="I41" s="7" t="inlineStr">
-        <is>
-          <t>冷酒（10～15℃前後）</t>
-        </is>
-      </c>
-      <c r="J41" s="7" t="inlineStr">
-        <is>
-          <t>日本酒情報DB</t>
-        </is>
-      </c>
-      <c r="K41" s="8" t="inlineStr">
-        <is>
-          <t>https://www.sakenomy.jp/sake/TST0000007476/</t>
-        </is>
-      </c>
+      <c r="J41" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="7" t="inlineStr"/>
       <c r="L41" s="7" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr">
         <is>
+          <t>冷酒（10～15℃前後）</t>
+        </is>
+      </c>
+      <c r="N41" s="7" t="inlineStr">
+        <is>
+          <t>日本酒情報DB</t>
+        </is>
+      </c>
+      <c r="O41" s="8" t="inlineStr">
+        <is>
+          <t>https://www.sakenomy.jp/sake/TST0000007476/</t>
+        </is>
+      </c>
+      <c r="P41" s="7" t="inlineStr"/>
+      <c r="Q41" s="7" t="inlineStr">
+        <is>
           <t>720ml / 1,800ml</t>
         </is>
       </c>
-      <c r="N41" s="7" t="inlineStr">
+      <c r="R41" s="7" t="inlineStr">
         <is>
           <t>3,300～11,000円</t>
         </is>
       </c>
-      <c r="O41" s="7" t="inlineStr">
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="P41" s="7" t="inlineStr">
+      <c r="T41" s="7" t="inlineStr">
         <is>
           <t>公式定番ラインナップ掲載 / 二次DBでも存在確認</t>
         </is>
       </c>
-      <c r="Q41" s="8" t="inlineStr">
+      <c r="U41" s="8" t="inlineStr">
         <is>
           <t>https://www.kamokin.com/line_up/regular.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Q41"/>
+  <autoFilter ref="A4:U41"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A2:U2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U12" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U14" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U15" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U16" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U17" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U18" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U19" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U20" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U21" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U22" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U23" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U24" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U25" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U26" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U27" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U28" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U29" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U30" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U31" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U32" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U33" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U34" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U35" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U36" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U37" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U38" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U39" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U40" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U41" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -3762,7 +6643,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3949,13 +6830,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6568,8 +9449,54 @@
       </c>
       <c r="E102" s="9" t="inlineStr"/>
     </row>
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>金光酒造</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>金光酒造 桜吹雪 純米大吟醸 1.8L</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>未採用</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>一般流通の商品単位へ確実に対応づけられないため本表には不採用</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>金光酒造</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>金光酒造 桜吹雪 純米大吟醸 720ml</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>未採用</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>一般流通の商品単位へ確実に対応づけられないため本表には不採用</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E102"/>
+  <autoFilter ref="A4:E104"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>

--- a/東広島市_安芸津・黒瀬エリア3蔵_現行日本酒一覧.xlsx
+++ b/東広島市_安芸津・黒瀬エリア3蔵_現行日本酒一覧.xlsx
@@ -211,7 +211,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_573163" displayName="T_573163" ref="A4:H10" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_515919" displayName="T_515919" ref="A4:H10" headerRowCount="1">
   <autoFilter ref="A4:H10"/>
   <tableColumns count="8">
     <tableColumn id="1" name="エリア"/>
@@ -228,7 +228,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_839278" displayName="T_839278" ref="A4:R25" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_845705" displayName="T_845705" ref="A4:R25" headerRowCount="1">
   <autoFilter ref="A4:R25"/>
   <tableColumns count="18">
     <tableColumn id="1" name="エリア"/>
@@ -255,7 +255,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T_270883" displayName="T_270883" ref="A4:U41" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T_219375" displayName="T_219375" ref="A4:U41" headerRowCount="1">
   <autoFilter ref="A4:U41"/>
   <tableColumns count="21">
     <tableColumn id="1" name="酒蔵"/>
@@ -285,7 +285,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T_900946" displayName="T_900946" ref="A4:I7" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T_474922" displayName="T_474922" ref="A4:I7" headerRowCount="1">
   <autoFilter ref="A4:I7"/>
   <tableColumns count="9">
     <tableColumn id="1" name="酒蔵"/>
@@ -303,7 +303,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T_964804" displayName="T_964804" ref="A4:E104" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T_853305" displayName="T_853305" ref="A4:E104" headerRowCount="1">
   <autoFilter ref="A4:E104"/>
   <tableColumns count="5">
     <tableColumn id="1" name="酒蔵"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="P6" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q6" s="9" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="P8" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q8" s="9" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="P10" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q10" s="9" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="P12" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q12" s="9" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="P14" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q14" s="9" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="P16" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q16" s="9" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="P18" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q18" s="9" t="inlineStr">
@@ -2452,7 +2452,7 @@
       <c r="L19" s="7" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>冷酒 / 常温 / 熱燗</t>
+          <t>冷酒 / 常温</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="R19" s="7" t="inlineStr">
         <is>
-          <t>https://www.tsukasyuzou.jp/products/於多福-純米-1800ml</t>
+          <t>https://www.tsukasyuzou.jp/products/火入れ-9代目於多福-純米大吟醸-720ml-1800ml</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       <c r="L20" s="9" t="inlineStr"/>
       <c r="M20" s="9" t="inlineStr">
         <is>
-          <t>冷酒 / 常温 / 熱燗</t>
+          <t>冷酒 / 常温 / ロック</t>
         </is>
       </c>
       <c r="N20" s="9" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="P20" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q20" s="9" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="R20" s="9" t="inlineStr">
         <is>
-          <t>https://www.tsukasyuzou.jp/products/於多福-純米-1800ml</t>
+          <t>https://www.tsukasyuzou.jp/products/9代目於多福-すずかぜ-720ml</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="P22" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q22" s="9" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="P24" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q24" s="9" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
@@ -4237,14 +4237,10 @@
       <c r="C17" s="7" t="inlineStr"/>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>公式が唯一醸す八反草の中心ライン</t>
-        </is>
-      </c>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr"/>
       <c r="F17" s="7" t="inlineStr">
         <is>
           <t>八反草 純米吟醸 ハイブリッド生酛</t>
@@ -5544,7 +5540,7 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>現行中心シリーズの上位酒</t>
+          <t>従来主ブランドの主要商品</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
